--- a/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_TEMPLATE_CATALOG.xlsx
+++ b/clients/healthcare-demo-new/19-template-instantiation-source-corpus/01-template-workbooks/HC_TEMPLATE_CATALOG.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Catalog" sheetId="1" r:id="R6c1dfa9ac3244845"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Healthcare Overlay" sheetId="2" r:id="R7dac8ca20e9c4c24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generated Outputs" sheetId="3" r:id="R01a849f363de4ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Catalog" sheetId="1" r:id="Rd74da0726e4a4440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Healthcare Overlay" sheetId="2" r:id="R0da7e7a09fb44197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generated Outputs" sheetId="3" r:id="R94bdadc5cff54cb5"/>
   </x:sheets>
 </x:workbook>
 </file>
